--- a/diseases/d126/2010-2014.xlsx
+++ b/diseases/d126/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1499,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1792,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2097,9 +2085,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2378,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2671,6 @@
       <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.0082018756356774</v>
       </c>
@@ -2985,9 +2964,6 @@
       <c r="O17" t="n">
         <v>20</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.041009378178387</v>
       </c>
@@ -3281,9 +3257,6 @@
       <c r="O19" t="n">
         <v>32</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.0656150050854192</v>
       </c>
@@ -3577,9 +3550,6 @@
       <c r="O21" t="n">
         <v>14</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.0287065647248709</v>
       </c>
@@ -3873,9 +3843,6 @@
       <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -4169,9 +4136,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4465,9 +4429,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4722,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5057,9 +5015,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5353,9 +5308,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5649,9 +5601,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -5945,9 +5894,6 @@
       <c r="O37" t="n">
         <v>2</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -6241,9 +6187,6 @@
       <c r="O39" t="n">
         <v>4</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.008142055500789488</v>
       </c>
@@ -6537,9 +6480,6 @@
       <c r="O41" t="n">
         <v>21</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.04274579137914482</v>
       </c>
@@ -6833,9 +6773,6 @@
       <c r="O43" t="n">
         <v>20</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.04071027750394745</v>
       </c>
@@ -7129,9 +7066,6 @@
       <c r="O45" t="n">
         <v>3</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.006106541625592117</v>
       </c>
@@ -7425,9 +7359,6 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -7721,9 +7652,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8017,9 +7945,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8313,9 +8238,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8609,9 +8531,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -8905,9 +8824,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9201,9 +9117,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -9497,9 +9410,6 @@
       <c r="O61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -9793,9 +9703,6 @@
       <c r="O63" t="n">
         <v>5</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.01008073062393603</v>
       </c>
@@ -10089,9 +9996,6 @@
       <c r="O65" t="n">
         <v>10</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.02016146124787207</v>
       </c>
@@ -10385,9 +10289,6 @@
       <c r="O67" t="n">
         <v>28</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.0564520914940418</v>
       </c>
@@ -10681,9 +10582,6 @@
       <c r="O69" t="n">
         <v>16</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.03225833799659531</v>
       </c>
@@ -10977,9 +10875,6 @@
       <c r="O71" t="n">
         <v>2</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -11273,9 +11168,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11569,9 +11461,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -11865,9 +11754,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12161,9 +12047,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12457,9 +12340,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -12753,9 +12633,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13049,9 +12926,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13345,9 +13219,6 @@
       <c r="O87" t="n">
         <v>5</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.009985787328752859</v>
       </c>
@@ -13641,9 +13512,6 @@
       <c r="O89" t="n">
         <v>12</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.02396588958900686</v>
       </c>
@@ -13937,9 +13805,6 @@
       <c r="O91" t="n">
         <v>23</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.04593462171226315</v>
       </c>
@@ -14233,9 +14098,6 @@
       <c r="O93" t="n">
         <v>15</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.02995736198625858</v>
       </c>
@@ -14529,9 +14391,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -14825,9 +14684,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15121,9 +14977,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15270,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -15713,9 +15563,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16009,9 +15856,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16305,9 +16149,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -16601,9 +16442,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -16897,9 +16735,6 @@
       <c r="O111" t="n">
         <v>6</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.01187200659102147</v>
       </c>
@@ -17193,9 +17028,6 @@
       <c r="O113" t="n">
         <v>10</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.01978667765170245</v>
       </c>
@@ -17489,9 +17321,6 @@
       <c r="O115" t="n">
         <v>32</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.06331736848544786</v>
       </c>
@@ -17785,9 +17614,6 @@
       <c r="O117" t="n">
         <v>9</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.01780800988653221</v>
       </c>
@@ -18081,9 +17907,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18376,9 +18199,6 @@
       </c>
       <c r="O121" t="n">
         <v>1</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0.001978667765170246</v>
